--- a/research/traditional_assets/database/data/netherlands/netherlands_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_environmental_waste_services.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -597,25 +597,25 @@
         <v>1.460194174757282</v>
       </c>
       <c r="I2">
-        <v>-0.5456310679611651</v>
+        <v>-7.788349514563107</v>
       </c>
       <c r="J2">
-        <v>-0.5456310679611651</v>
+        <v>-7.788349514563107</v>
       </c>
       <c r="K2">
-        <v>-0.477</v>
+        <v>-4.257</v>
       </c>
       <c r="L2">
-        <v>-0.9262135922330097</v>
+        <v>-8.266019417475727</v>
       </c>
       <c r="M2">
         <v>1.19</v>
       </c>
       <c r="N2">
-        <v>0.09999999999999999</v>
+        <v>0.03366336633663366</v>
       </c>
       <c r="O2">
-        <v>-2.49475890985325</v>
+        <v>-0.2795395818651633</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -633,31 +633,31 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>0.253</v>
+        <v>10.853</v>
       </c>
       <c r="V2">
-        <v>0.02126050420168067</v>
+        <v>0.307015558698727</v>
       </c>
       <c r="W2">
-        <v>-0.075</v>
+        <v>-0.09846774193548387</v>
       </c>
       <c r="X2">
-        <v>0.05254888351732016</v>
+        <v>0.0934830579321836</v>
       </c>
       <c r="Y2">
-        <v>-0.1275488835173202</v>
+        <v>-0.1919507998676675</v>
       </c>
       <c r="Z2">
-        <v>0.1239172281039461</v>
+        <v>0.02011247363899086</v>
       </c>
       <c r="AA2">
-        <v>-0.0676130895091434</v>
+        <v>-0.1207529317009587</v>
       </c>
       <c r="AB2">
-        <v>0.05077337907214942</v>
+        <v>0.09172734514045856</v>
       </c>
       <c r="AC2">
-        <v>-0.1183864685812928</v>
+        <v>-0.2124802768414172</v>
       </c>
       <c r="AD2">
         <v>0.709</v>
@@ -669,37 +669,37 @@
         <v>0.709</v>
       </c>
       <c r="AG2">
-        <v>0.456</v>
+        <v>-10.144</v>
       </c>
       <c r="AH2">
-        <v>0.05622967721468792</v>
+        <v>0.01966222025014559</v>
       </c>
       <c r="AI2">
-        <v>0.08689790415492094</v>
+        <v>0.01460079490928561</v>
       </c>
       <c r="AJ2">
-        <v>0.03690514729685982</v>
+        <v>-0.4024438625724033</v>
       </c>
       <c r="AK2">
-        <v>0.0576777131292689</v>
+        <v>-0.2690288017822097</v>
       </c>
       <c r="AL2">
-        <v>0.066</v>
+        <v>0.109</v>
       </c>
       <c r="AM2">
-        <v>-0.107</v>
+        <v>-0.06499999999999999</v>
       </c>
       <c r="AN2">
         <v>-2.685606060606061</v>
       </c>
       <c r="AO2">
-        <v>-4.257575757575758</v>
+        <v>-36.79816513761468</v>
       </c>
       <c r="AP2">
-        <v>-1.727272727272727</v>
+        <v>38.42424242424242</v>
       </c>
       <c r="AQ2">
-        <v>2.626168224299066</v>
+        <v>61.70769230769232</v>
       </c>
     </row>
     <row r="3">
@@ -743,7 +743,7 @@
         <v>1.19</v>
       </c>
       <c r="N3">
-        <v>0.09999999999999999</v>
+        <v>0.1233160621761658</v>
       </c>
       <c r="O3">
         <v>-2.49475890985325</v>
@@ -767,16 +767,16 @@
         <v>0.253</v>
       </c>
       <c r="V3">
-        <v>0.02126050420168067</v>
+        <v>0.02621761658031088</v>
       </c>
       <c r="W3">
         <v>-0.075</v>
       </c>
       <c r="X3">
-        <v>0.05254888351732016</v>
+        <v>0.09493405362335597</v>
       </c>
       <c r="Y3">
-        <v>-0.1275488835173202</v>
+        <v>-0.169934053623356</v>
       </c>
       <c r="Z3">
         <v>0.1239172281039461</v>
@@ -785,10 +785,10 @@
         <v>-0.0676130895091434</v>
       </c>
       <c r="AB3">
-        <v>0.05077337907214942</v>
+        <v>0.09142262803990589</v>
       </c>
       <c r="AC3">
-        <v>-0.1183864685812928</v>
+        <v>-0.1590357175490493</v>
       </c>
       <c r="AD3">
         <v>0.709</v>
@@ -803,13 +803,13 @@
         <v>0.456</v>
       </c>
       <c r="AH3">
-        <v>0.05622967721468792</v>
+        <v>0.06844289989381214</v>
       </c>
       <c r="AI3">
         <v>0.08689790415492094</v>
       </c>
       <c r="AJ3">
-        <v>0.03690514729685982</v>
+        <v>0.04512170987532159</v>
       </c>
       <c r="AK3">
         <v>0.0576777131292689</v>
@@ -831,6 +831,110 @@
       </c>
       <c r="AQ3">
         <v>2.626168224299066</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pryme N.V. (OB:PRYME)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Waste Services</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-3.78</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>10.6</v>
+      </c>
+      <c r="V4">
+        <v>0.4124513618677043</v>
+      </c>
+      <c r="W4">
+        <v>-0.1219354838709677</v>
+      </c>
+      <c r="X4">
+        <v>0.09203206224101124</v>
+      </c>
+      <c r="Y4">
+        <v>-0.213967546111979</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-0.1738927738927739</v>
+      </c>
+      <c r="AB4">
+        <v>0.09203206224101124</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2659248361337851</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-10.6</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.7019867549668874</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3557046979865772</v>
+      </c>
+      <c r="AL4">
+        <v>0.043</v>
+      </c>
+      <c r="AM4">
+        <v>0.042</v>
+      </c>
+      <c r="AO4">
+        <v>-86.74418604651163</v>
+      </c>
+      <c r="AQ4">
+        <v>-88.80952380952382</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_environmental_waste_services.xlsx
@@ -587,35 +587,32 @@
           <t>Environmental &amp; Waste Services</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.491</v>
-      </c>
       <c r="G2">
-        <v>1.460194174757282</v>
+        <v>-0.8</v>
       </c>
       <c r="H2">
-        <v>1.460194174757282</v>
+        <v>-0.8</v>
       </c>
       <c r="I2">
-        <v>-7.788349514563107</v>
+        <v>-6.51111111111111</v>
       </c>
       <c r="J2">
-        <v>-7.788349514563107</v>
+        <v>-6.51111111111111</v>
       </c>
       <c r="K2">
-        <v>-4.257</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L2">
-        <v>-8.266019417475727</v>
+        <v>-6.51111111111111</v>
       </c>
       <c r="M2">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>0.03366336633663366</v>
+        <v>0.01758969000348311</v>
       </c>
       <c r="O2">
-        <v>-0.2795395818651633</v>
+        <v>-0.1149032992036405</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>10.853</v>
+        <v>14.05</v>
       </c>
       <c r="V2">
-        <v>0.307015558698727</v>
+        <v>0.2446882619296412</v>
       </c>
       <c r="W2">
-        <v>-0.09846774193548387</v>
+        <v>-0.1966922187813495</v>
       </c>
       <c r="X2">
-        <v>0.0934830579321836</v>
+        <v>0.08997853582679242</v>
       </c>
       <c r="Y2">
-        <v>-0.1919507998676675</v>
+        <v>-0.286670754608142</v>
       </c>
       <c r="Z2">
-        <v>0.02011247363899086</v>
+        <v>0.03641660597232339</v>
       </c>
       <c r="AA2">
-        <v>-0.1207529317009587</v>
+        <v>-0.219226397225717</v>
       </c>
       <c r="AB2">
-        <v>0.09172734514045856</v>
+        <v>0.07315218167847573</v>
       </c>
       <c r="AC2">
-        <v>-0.2124802768414172</v>
+        <v>-0.2923785789041927</v>
       </c>
       <c r="AD2">
-        <v>0.709</v>
+        <v>17.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.709</v>
+        <v>17.8</v>
       </c>
       <c r="AG2">
-        <v>-10.144</v>
+        <v>3.749999999999996</v>
       </c>
       <c r="AH2">
-        <v>0.01966222025014559</v>
+        <v>0.2366391917043339</v>
       </c>
       <c r="AI2">
-        <v>0.01460079490928561</v>
+        <v>0.1844559585492228</v>
       </c>
       <c r="AJ2">
-        <v>-0.4024438625724033</v>
+        <v>0.06130456105934275</v>
       </c>
       <c r="AK2">
-        <v>-0.2690288017822097</v>
+        <v>0.04548211036992112</v>
       </c>
       <c r="AL2">
-        <v>0.109</v>
+        <v>0.31</v>
       </c>
       <c r="AM2">
-        <v>-0.06499999999999999</v>
+        <v>-0.109</v>
       </c>
       <c r="AN2">
-        <v>-2.685606060606061</v>
+        <v>-13.48484848484848</v>
       </c>
       <c r="AO2">
-        <v>-36.79816513761468</v>
+        <v>-28.35483870967742</v>
       </c>
       <c r="AP2">
-        <v>38.42424242424242</v>
+        <v>-2.840909090909088</v>
       </c>
       <c r="AQ2">
-        <v>61.70769230769232</v>
+        <v>80.64220183486239</v>
       </c>
     </row>
     <row r="3">
@@ -718,35 +715,32 @@
           <t>Environmental &amp; Waste Services</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.491</v>
-      </c>
       <c r="G3">
-        <v>1.460194174757282</v>
+        <v>-0.8</v>
       </c>
       <c r="H3">
-        <v>1.460194174757282</v>
+        <v>-0.8</v>
       </c>
       <c r="I3">
-        <v>-0.5456310679611651</v>
+        <v>-1.022222222222222</v>
       </c>
       <c r="J3">
-        <v>-0.5456310679611651</v>
+        <v>-1.022222222222222</v>
       </c>
       <c r="K3">
-        <v>-0.477</v>
+        <v>-1.44</v>
       </c>
       <c r="L3">
-        <v>-0.9262135922330097</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="M3">
-        <v>1.19</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1233160621761658</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-2.49475890985325</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +752,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>1.19</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.253</v>
+        <v>0.05</v>
       </c>
       <c r="V3">
-        <v>0.02621761658031088</v>
+        <v>0.008445945945945946</v>
       </c>
       <c r="W3">
-        <v>-0.075</v>
+        <v>-0.2114537444933921</v>
       </c>
       <c r="X3">
-        <v>0.09493405362335597</v>
+        <v>0.09712555854457361</v>
       </c>
       <c r="Y3">
-        <v>-0.169934053623356</v>
+        <v>-0.3085793030379657</v>
       </c>
       <c r="Z3">
-        <v>0.1239172281039461</v>
+        <v>0.1856690964103975</v>
       </c>
       <c r="AA3">
-        <v>-0.0676130895091434</v>
+        <v>-0.1897950763306285</v>
       </c>
       <c r="AB3">
-        <v>0.09142262803990589</v>
+        <v>0.07115604492242165</v>
       </c>
       <c r="AC3">
-        <v>-0.1590357175490493</v>
+        <v>-0.2609511212530502</v>
       </c>
       <c r="AD3">
-        <v>0.709</v>
+        <v>4.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.709</v>
+        <v>4.6</v>
       </c>
       <c r="AG3">
-        <v>0.456</v>
+        <v>4.55</v>
       </c>
       <c r="AH3">
-        <v>0.06844289989381214</v>
+        <v>0.4372623574144486</v>
       </c>
       <c r="AI3">
-        <v>0.08689790415492094</v>
+        <v>0.1474358974358974</v>
       </c>
       <c r="AJ3">
-        <v>0.04512170987532159</v>
+        <v>0.4345749761222541</v>
       </c>
       <c r="AK3">
-        <v>0.0576777131292689</v>
+        <v>0.1460674157303371</v>
       </c>
       <c r="AL3">
-        <v>0.066</v>
+        <v>0.16</v>
       </c>
       <c r="AM3">
-        <v>-0.107</v>
+        <v>-0.04899999999999999</v>
       </c>
       <c r="AN3">
-        <v>-2.685606060606061</v>
+        <v>-3.484848484848484</v>
       </c>
       <c r="AO3">
-        <v>-4.257575757575758</v>
+        <v>-8.625</v>
       </c>
       <c r="AP3">
-        <v>-1.727272727272727</v>
+        <v>-3.446969696969697</v>
       </c>
       <c r="AQ3">
-        <v>2.626168224299066</v>
+        <v>28.16326530612245</v>
       </c>
     </row>
     <row r="4">
@@ -850,16 +841,16 @@
         </is>
       </c>
       <c r="K4">
-        <v>-3.78</v>
+        <v>-7.35</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.01961165048543689</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.1374149659863946</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -871,70 +862,73 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.01</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>10.6</v>
+        <v>14</v>
       </c>
       <c r="V4">
-        <v>0.4124513618677043</v>
+        <v>0.2718446601941747</v>
       </c>
       <c r="W4">
-        <v>-0.1219354838709677</v>
+        <v>-0.1819306930693069</v>
       </c>
       <c r="X4">
-        <v>0.09203206224101124</v>
+        <v>0.08283151310901124</v>
       </c>
       <c r="Y4">
-        <v>-0.213967546111979</v>
+        <v>-0.2647622061783181</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.1738927738927739</v>
+        <v>-0.2486577181208054</v>
       </c>
       <c r="AB4">
-        <v>0.09203206224101124</v>
+        <v>0.07514831843452982</v>
       </c>
       <c r="AC4">
-        <v>-0.2659248361337851</v>
+        <v>-0.3238060365553352</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="AG4">
-        <v>-10.6</v>
+        <v>-0.8000000000000007</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2040185471406491</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.2021439509954058</v>
       </c>
       <c r="AJ4">
-        <v>-0.7019867549668874</v>
+        <v>-0.01577909270216964</v>
       </c>
       <c r="AK4">
-        <v>-0.3557046979865772</v>
+        <v>-0.0155945419103314</v>
       </c>
       <c r="AL4">
-        <v>0.043</v>
+        <v>0.15</v>
       </c>
       <c r="AM4">
-        <v>0.042</v>
+        <v>-0.06</v>
       </c>
       <c r="AO4">
-        <v>-86.74418604651163</v>
+        <v>-49.40000000000001</v>
       </c>
       <c r="AQ4">
-        <v>-88.80952380952382</v>
+        <v>123.5</v>
       </c>
     </row>
   </sheetData>
